--- a/quizzes/sculpture-14e.xlsx
+++ b/quizzes/sculpture-14e.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers simplifiés\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0909613-FA71-44FA-88B4-E7E737BAA63E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="203">
   <si>
     <t>Prénom</t>
   </si>
@@ -313,9 +319,6 @@
     <t>Florence</t>
   </si>
   <si>
-    <t>Saint-Denis</t>
-  </si>
-  <si>
     <t>Milan</t>
   </si>
   <si>
@@ -340,15 +343,9 @@
     <t>Naples</t>
   </si>
   <si>
-    <t>Orvieto</t>
-  </si>
-  <si>
     <t>Prague</t>
   </si>
   <si>
-    <t>Saint Denis</t>
-  </si>
-  <si>
     <t>Dijon</t>
   </si>
   <si>
@@ -358,9 +355,6 @@
     <t>Basilique de Saint-Denis</t>
   </si>
   <si>
-    <t>Chapelle des Comtes (Gravenkapel) dans l’église Notre-Dame de Courtrai</t>
-  </si>
-  <si>
     <t>Cathédrale de Florence</t>
   </si>
   <si>
@@ -632,13 +626,16 @@
   </si>
   <si>
     <t>néerlandaise</t>
+  </si>
+  <si>
+    <t>Chapelle des Comtes  dans l’église Notre-Dame de Courtrai</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -683,18 +680,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -732,7 +737,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -766,6 +771,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -800,9 +806,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -975,11 +982,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1053,7 +1060,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -1070,25 +1077,25 @@
         <v>98</v>
       </c>
       <c r="J2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="M2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="S2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="W2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="X2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -1104,29 +1111,26 @@
       <c r="H3" t="s">
         <v>75</v>
       </c>
-      <c r="I3" t="s">
-        <v>99</v>
-      </c>
       <c r="J3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="M3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="S3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="W3" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="X3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -1143,28 +1147,28 @@
         <v>76</v>
       </c>
       <c r="J4" t="s">
-        <v>114</v>
+        <v>202</v>
       </c>
       <c r="M4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="S4" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="T4" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="W4" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="X4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -1174,29 +1178,26 @@
       <c r="H5" t="s">
         <v>77</v>
       </c>
-      <c r="I5" t="s">
-        <v>98</v>
-      </c>
       <c r="J5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="M5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="S5" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="W5" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="X5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -1210,28 +1211,28 @@
         <v>78</v>
       </c>
       <c r="I6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="S6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="W6" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="X6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -1245,28 +1246,28 @@
         <v>79</v>
       </c>
       <c r="I7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J7" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M7" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="S7" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="W7" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="X7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1280,28 +1281,28 @@
         <v>80</v>
       </c>
       <c r="I8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J8" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="M8" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="S8" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="W8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="X8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -1315,28 +1316,28 @@
         <v>81</v>
       </c>
       <c r="I9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="M9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="S9" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="W9" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="X9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1353,34 +1354,34 @@
         <v>60</v>
       </c>
       <c r="I10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J10" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="M10" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="S10" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="T10" t="s">
+        <v>194</v>
+      </c>
+      <c r="U10" t="s">
+        <v>197</v>
+      </c>
+      <c r="W10" t="s">
         <v>198</v>
       </c>
-      <c r="U10" t="s">
-        <v>201</v>
-      </c>
-      <c r="W10" t="s">
-        <v>202</v>
-      </c>
       <c r="X10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1397,28 +1398,28 @@
         <v>82</v>
       </c>
       <c r="I11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J11" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="M11" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="S11" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="W11" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="X11">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -1434,29 +1435,26 @@
       <c r="H12" t="s">
         <v>83</v>
       </c>
-      <c r="I12" t="s">
-        <v>106</v>
-      </c>
       <c r="J12" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="M12" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="S12" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="W12" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="X12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -1473,28 +1471,28 @@
         <v>84</v>
       </c>
       <c r="I13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J13" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="M13" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="S13" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="W13" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="X13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -1520,25 +1518,25 @@
         <v>98</v>
       </c>
       <c r="J14" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="S14" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="W14" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="X14">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -1549,28 +1547,28 @@
         <v>86</v>
       </c>
       <c r="I15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J15" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="M15" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="S15" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="W15" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="X15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -1586,29 +1584,26 @@
       <c r="H16" t="s">
         <v>87</v>
       </c>
-      <c r="I16" t="s">
-        <v>108</v>
-      </c>
       <c r="J16" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="M16" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="S16" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="W16" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="X16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -1625,28 +1620,28 @@
         <v>88</v>
       </c>
       <c r="I17" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J17" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="M17" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="S17" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="W17" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="X17">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -1663,28 +1658,28 @@
         <v>88</v>
       </c>
       <c r="I18" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J18" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="M18" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="S18" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="W18" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="X18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -1697,29 +1692,26 @@
       <c r="H19" t="s">
         <v>86</v>
       </c>
-      <c r="I19" t="s">
-        <v>110</v>
-      </c>
       <c r="J19" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="M19" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="S19" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="W19" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="X19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>30</v>
       </c>
@@ -1739,25 +1731,25 @@
         <v>98</v>
       </c>
       <c r="J20" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="M20" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="S20" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="W20" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="X20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -1777,25 +1769,25 @@
         <v>98</v>
       </c>
       <c r="J21" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="M21" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="S21" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="W21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="X21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -1811,29 +1803,26 @@
       <c r="H22" t="s">
         <v>91</v>
       </c>
-      <c r="I22" t="s">
-        <v>105</v>
-      </c>
       <c r="J22" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="M22" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="S22" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="W22" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="X22">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -1849,29 +1838,26 @@
       <c r="H23" t="s">
         <v>92</v>
       </c>
-      <c r="I23" t="s">
-        <v>105</v>
-      </c>
       <c r="J23" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="M23" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="S23" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="W23" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="X23">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1887,29 +1873,26 @@
       <c r="H24" t="s">
         <v>92</v>
       </c>
-      <c r="I24" t="s">
-        <v>105</v>
-      </c>
       <c r="J24" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="M24" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="S24" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="W24" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="X24">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -1925,32 +1908,29 @@
       <c r="H25" t="s">
         <v>92</v>
       </c>
-      <c r="I25" t="s">
-        <v>105</v>
-      </c>
       <c r="J25" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="M25" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="S25" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="T25" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="W25" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="X25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -1967,28 +1947,28 @@
         <v>98</v>
       </c>
       <c r="J26" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="M26" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="S26" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="T26" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="W26" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="X26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -2005,28 +1985,28 @@
         <v>94</v>
       </c>
       <c r="I27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J27" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="M27" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="S27" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="W27" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="X27">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -2043,28 +2023,28 @@
         <v>95</v>
       </c>
       <c r="I28" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J28" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="M28" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="N28" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="S28" t="s">
         <v>189</v>
       </c>
-      <c r="S28" t="s">
-        <v>193</v>
-      </c>
       <c r="W28" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="X28">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>35</v>
       </c>
@@ -2081,31 +2061,31 @@
         <v>96</v>
       </c>
       <c r="I29" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="J29" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="M29" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="S29" t="s">
+        <v>192</v>
+      </c>
+      <c r="T29" t="s">
         <v>196</v>
       </c>
-      <c r="T29" t="s">
-        <v>200</v>
-      </c>
       <c r="W29" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="X29">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>36</v>
       </c>
@@ -2116,22 +2096,22 @@
         <v>97</v>
       </c>
       <c r="I30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J30" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="M30" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="S30" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="W30" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="X30">
         <v>1</v>
@@ -2139,35 +2119,35 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="N2" r:id="rId1"/>
-    <hyperlink ref="N3" r:id="rId2"/>
-    <hyperlink ref="N4" r:id="rId3"/>
-    <hyperlink ref="N5" r:id="rId4"/>
-    <hyperlink ref="N6" r:id="rId5"/>
-    <hyperlink ref="N7" r:id="rId6"/>
-    <hyperlink ref="N8" r:id="rId7"/>
-    <hyperlink ref="N9" r:id="rId8"/>
-    <hyperlink ref="N10" r:id="rId9"/>
-    <hyperlink ref="N11" r:id="rId10"/>
-    <hyperlink ref="N12" r:id="rId11"/>
-    <hyperlink ref="N13" r:id="rId12"/>
-    <hyperlink ref="N14" r:id="rId13"/>
-    <hyperlink ref="N15" r:id="rId14"/>
-    <hyperlink ref="N16" r:id="rId15"/>
-    <hyperlink ref="N17" r:id="rId16"/>
-    <hyperlink ref="N18" r:id="rId17"/>
-    <hyperlink ref="N19" r:id="rId18"/>
-    <hyperlink ref="N20" r:id="rId19"/>
-    <hyperlink ref="N21" r:id="rId20"/>
-    <hyperlink ref="N22" r:id="rId21"/>
-    <hyperlink ref="N23" r:id="rId22"/>
-    <hyperlink ref="N24" r:id="rId23"/>
-    <hyperlink ref="N25" r:id="rId24"/>
-    <hyperlink ref="N26" r:id="rId25"/>
-    <hyperlink ref="N27" r:id="rId26"/>
-    <hyperlink ref="N28" r:id="rId27"/>
-    <hyperlink ref="N29" r:id="rId28"/>
-    <hyperlink ref="N30" r:id="rId29"/>
+    <hyperlink ref="N2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="N3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="N4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="N5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="N6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="N7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="N8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="N9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="N10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="N11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="N12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="N13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="N14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="N15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="N16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="N17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="N18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="N19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="N20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="N21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="N22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="N23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="N24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="N25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="N26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="N27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="N28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="N29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="N30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-14e.xlsx
+++ b/quizzes/sculpture-14e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CA785C-3E8B-4C1F-9F8A-6378B83B8583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B840689-C483-450A-BA63-30FD0BE99D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1939,16 +1939,6 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:V34">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>IFERROR(--$V2,0)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W34">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>IFERROR(--$V2,0)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="K2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="K7" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>

--- a/quizzes/sculpture-14e.xlsx
+++ b/quizzes/sculpture-14e.xlsx
@@ -32,12 +32,17 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -56,12 +61,13 @@
       <protection locked="0" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -618,6 +624,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1f/Alberto_Arnoldi%2C_madonna_col_bambino_tra_i_ss._pietro_martire_e_lucia%2C_post_1351%2C_01.JPG/1280px-Alberto_Arnoldi%2C_madonna_col_bambino_tra_i_ss._pietro_martire_e_lucia%2C_post_1351%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>Ronde-bosse</t>
+        </is>
+      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>Marbre</t>
@@ -725,6 +736,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/21/Statue_of_Saint_Catherine_Gravenkapel_Kortrijk_17052015_5.jpg/1280px-Statue_of_Saint_Catherine_Gravenkapel_Kortrijk_17052015_5.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Ronde-bosse</t>
+        </is>
+      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>Marbre</t>
@@ -775,6 +791,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bb/Firenze_Cattedrale_di_Santa_Maria_del_Fiore_Esterno_Lato_Nord_Portale_Timpano_2.jpg/1280px-Firenze_Cattedrale_di_Santa_Maria_del_Fiore_Esterno_Lato_Nord_Portale_Timpano_2.jpg</t>
         </is>
       </c>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>Elément architectural</t>
+        </is>
+      </c>
       <c r="S9" t="inlineStr">
         <is>
           <t>Marbre</t>
@@ -1051,6 +1072,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4d/Presentation_Scene_with_Saint_Peter_Martyr_and_Three_Donors_MET_DT4966.jpg/1280px-Presentation_Scene_with_Saint_Peter_Martyr_and_Three_Donors_MET_DT4966.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Bas-relief</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>Marbre</t>
@@ -1111,6 +1137,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/e5/Escultures_del_monument_f%C3%BAnebre_d%27Enric_VII%2C_Tina_di_Camaino%2C_Museo_dell%27Opera_del_Duomo%2C_Pisa.JPG/1280px-Escultures_del_monument_f%C3%BAnebre_d%27Enric_VII%2C_Tina_di_Camaino%2C_Museo_dell%27Opera_del_Duomo%2C_Pisa.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Monument funéraire avec ronde-bosse</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr">
         <is>
           <t>Marbre</t>
@@ -1266,6 +1297,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/5/52/Tabernakel%2C_Andrea_di_Cione%2C_1359%2C_Orsanmichele_Florenz-01-185.jpg/960px-Tabernakel%2C_Andrea_di_Cione%2C_1359%2C_Orsanmichele_Florenz-01-185.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Mobilier liturgique</t>
+        </is>
+      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>Marbre</t>
@@ -1316,6 +1352,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1b/Camposanto-tabernacole-group-museo-opera-pisa.jpg/1280px-Camposanto-tabernacole-group-museo-opera-pisa.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Mobilier liturgique</t>
+        </is>
+      </c>
       <c r="S19" t="inlineStr">
         <is>
           <t>Marbre</t>
@@ -1361,6 +1402,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/fe/Orvieto059.jpg/1280px-Orvieto059.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>Elément architectural</t>
+        </is>
+      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>Marbre</t>
@@ -1411,6 +1457,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/c/cb/Busta_Petr_Parl%C3%A9%C5%99.jpg/1280px-Busta_Petr_Parl%C3%A9%C5%99.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>Buste</t>
+        </is>
+      </c>
       <c r="S21" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -1461,6 +1512,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/fa/Prag_Dom_St._Veit_07.jpg/1280px-Prag_Dom_St._Veit_07.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Elément architectural</t>
+        </is>
+      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -1561,6 +1617,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f6/South_Doors_of_the_Florence_Baptistry.JPG/1280px-South_Doors_of_the_Florence_Baptistry.JPG</t>
         </is>
       </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Elément architectural</t>
+        </is>
+      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>Bronze doré</t>
@@ -1611,6 +1672,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/67/Andrea_Pisano%2C_The_Creation_of_Adam_and_Eve%2C_1334-43%2C_Museo_dell%27Opera_del_Duomo%2C_Florence.jpg/1280px-Andrea_Pisano%2C_The_Creation_of_Adam_and_Eve%2C_1334-43%2C_Museo_dell%27Opera_del_Duomo%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>Elément architectural</t>
+        </is>
+      </c>
       <c r="S25" t="inlineStr">
         <is>
           <t>Marbre</t>
@@ -1656,6 +1722,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/06/Andrea_pisano%2C_madonna_col_bambino_%281346_ca.%29_tra_i_ss._pietro_e_paolo_attr._a_lupo_di_francesco_%281300-30_ca.%29%2C_dalla_facciata_del_duomo_di_pisa.jpg/1280px-Andrea_pisano%2C_madonna_col_bambino_%281346_ca.%29_tra_i_ss._pietro_e_paolo_attr._a_lupo_di_francesco_%281300-30_ca.%29%2C_dalla_facciata_del_duomo_di_pisa.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>Elément architectural</t>
+        </is>
+      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>Marbre</t>
@@ -1701,6 +1772,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/7/77/Cathedral_pulpit_-_Pisa.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Mobilier liturgique</t>
+        </is>
+      </c>
       <c r="S27" t="inlineStr">
         <is>
           <t>Marbre</t>
@@ -1746,6 +1822,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/37/Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_virt%C3%B9_teologali_%28fede%2C_speranza_e_carit%C3%A0%29_sulle_arti_del_trivio%2C_quadrivio_e_filosofia_03.JPG/1280px-Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_virt%C3%B9_teologali_%28fede%2C_speranza_e_carit%C3%A0%29_sulle_arti_del_trivio%2C_quadrivio_e_filosofia_03.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Mobilier liturgique</t>
+        </is>
+      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>Marbre</t>
@@ -1791,6 +1872,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f1/Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_stiloforo_02.JPG/1280px-Giovanni_pisano%2C_pulpito_del_duomo_di_pisa%2C_1302-11%2C_stiloforo_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Mobilier liturgique</t>
+        </is>
+      </c>
       <c r="S29" t="inlineStr">
         <is>
           <t>Marbre</t>
@@ -1846,6 +1932,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/a/a6/Nino_pisano%2C_sibilla_eritrea%2C_1337-41%2C_dal_lato_nord_del_campanile.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>Elément architectural</t>
+        </is>
+      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>Marbre</t>
@@ -1956,6 +2047,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/29/Dijon_-_Chapelle_du_centre_hospitalier_La_Chartreuse_-_2.jpg/1280px-Dijon_-_Chapelle_du_centre_hospitalier_La_Chartreuse_-_2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Elément architectural</t>
+        </is>
+      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>Pierre</t>
@@ -2006,6 +2102,11 @@
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/07/Well_of_Moses%2C_Champmol%2C_2010.JPG/1280px-Well_of_Moses%2C_Champmol%2C_2010.JPG</t>
         </is>
       </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>Monument avec ronde-bosse</t>
+        </is>
+      </c>
       <c r="S33" t="inlineStr">
         <is>
           <t>Pierre calcaire polychrome</t>
@@ -2059,6 +2160,11 @@
       <c r="L34" s="1" t="inlineStr">
         <is>
           <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/eb/Agnolo_di_ventura%2C_portale_della_cappella_petroni%2C_1336%2C_02_madonna_col_bambino_tra_s._francesco_e_il_beato_pietro_da_siena.jpg/1280px-Agnolo_di_ventura%2C_portale_della_cappella_petroni%2C_1336%2C_02_madonna_col_bambino_tra_s._francesco_e_il_beato_pietro_da_siena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Elément architectural</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
